--- a/SAP Reports/Input Files/P&L Jan 26/PL ITCURVES JAN 26 ANNUAL.xlsx
+++ b/SAP Reports/Input Files/P&L Jan 26/PL ITCURVES JAN 26 ANNUAL.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtariq.TGI\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C71E0F-F556-4CFE-94D0-6676DB9DCBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="25875" windowHeight="15135"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +34,7 @@
     <t>Revenues</t>
   </si>
   <si>
-    <t>$  208,200.00</t>
+    <t>$  210,825.00</t>
   </si>
   <si>
     <t>Income - Income</t>
@@ -37,7 +43,7 @@
     <t>Sales Revenue - SALES REVENUE</t>
   </si>
   <si>
-    <t>$  200,200.00</t>
+    <t>$  202,825.00</t>
   </si>
   <si>
     <t>408500-04-000-00 - WORLDPAY COMMISSION</t>
@@ -55,7 +61,7 @@
     <t>409200-04-000-00 - SAAS CLOUD</t>
   </si>
   <si>
-    <t>$  40,450.73</t>
+    <t>$  43,075.73</t>
   </si>
   <si>
     <t>409300-04-000-00 - CARRIER VOIP</t>
@@ -148,7 +154,7 @@
     <t>Gross Profit</t>
   </si>
   <si>
-    <t>$  197,404.77</t>
+    <t>$  200,029.77</t>
   </si>
   <si>
     <t>Expenses</t>
@@ -163,13 +169,7 @@
     <t>Payroll exp - SALARIES &amp; OVERHEADS</t>
   </si>
   <si>
-    <t>$ (50,276.35)</t>
-  </si>
-  <si>
-    <t>685000-04-000-00 - Professional Fee: Cloud Work</t>
-  </si>
-  <si>
-    <t>$ (1,149.00)</t>
+    <t>$ (49,127.35)</t>
   </si>
   <si>
     <t>701000-04-000-00 - MEDICAL INS EXP</t>
@@ -226,7 +226,7 @@
     <t>GeneralAdmin - GENERAL AND ADMINISTRATIVE EXPENSES</t>
   </si>
   <si>
-    <t>$ (34,428.54)</t>
+    <t>$ (35,577.54)</t>
   </si>
   <si>
     <t>621000-04-000-00 - CREDIT CARD MERCHANT CHG</t>
@@ -235,12 +235,6 @@
     <t>$ (109.52)</t>
   </si>
   <si>
-    <t>636000-04-000-00 - OFF SHORE DEVELOPMENT NCS</t>
-  </si>
-  <si>
-    <t>$ (12,500.00)</t>
-  </si>
-  <si>
     <t>645000-04-000-00 - DUES AND SUBSCRIPTIONS</t>
   </si>
   <si>
@@ -253,6 +247,18 @@
     <t>$ (6,687.50)</t>
   </si>
   <si>
+    <t>680000-04-000-00 - INTERNET GIGE PORT</t>
+  </si>
+  <si>
+    <t>$ (950.00)</t>
+  </si>
+  <si>
+    <t>685000-04-000-00 - PROFESSIONAL FEE: CLOUD WORK</t>
+  </si>
+  <si>
+    <t>$ (13,649.00)</t>
+  </si>
+  <si>
     <t>710000-04-000-00 - OFFICE EXPENSE &amp; SUPPLIES</t>
   </si>
   <si>
@@ -274,7 +280,7 @@
     <t>765000-04-000-00 - TELEPHONE EXPENSE</t>
   </si>
   <si>
-    <t>$ (2,158.98)</t>
+    <t>$ (1,208.98)</t>
   </si>
   <si>
     <t>780000-04-000-00 - UTILITIES EXPENSE</t>
@@ -301,7 +307,7 @@
     <t>Operating Profit</t>
   </si>
   <si>
-    <t>$  112,699.88</t>
+    <t>$  115,324.88</t>
   </si>
   <si>
     <t>Financing</t>
@@ -373,7 +379,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -900,13 +906,13 @@
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -923,14 +929,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -968,7 +977,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1040,7 +1049,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1213,9 +1222,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C158"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="70.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1226,7 +1241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1237,9 +1252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
-		</row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1250,9 +1263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5">
-		</row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1263,9 +1274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7">
-		</row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1276,7 +1285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1287,7 +1296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1298,7 +1307,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1309,7 +1318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1320,7 +1329,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1331,7 +1340,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>20</v>
       </c>
@@ -1339,7 +1348,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1350,7 +1359,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>22</v>
       </c>
@@ -1358,9 +1367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17">
-		</row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1371,9 +1378,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19">
-		</row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1384,7 +1389,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1395,7 +1400,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1406,7 +1411,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1417,7 +1422,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>20</v>
       </c>
@@ -1425,7 +1430,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1436,7 +1441,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>22</v>
       </c>
@@ -1444,7 +1449,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>20</v>
       </c>
@@ -1452,7 +1457,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1463,7 +1468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>22</v>
       </c>
@@ -1471,7 +1476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>20</v>
       </c>
@@ -1479,7 +1484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1490,9 +1495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32">
-		</row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -1503,9 +1506,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34">
-		</row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -1516,9 +1517,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36">
-		</row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1529,9 +1528,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38">
-		</row>
-    <row r="39">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1542,7 +1539,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>20</v>
       </c>
@@ -1550,7 +1547,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -1561,7 +1558,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>22</v>
       </c>
@@ -1569,16 +1566,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43">
-		</row>
-    <row r="44">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45">
-		</row>
-    <row r="46">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>20</v>
       </c>
@@ -1586,12 +1579,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>22</v>
       </c>
@@ -1599,7 +1592,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>20</v>
       </c>
@@ -1607,7 +1600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>41</v>
       </c>
@@ -1618,7 +1611,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>22</v>
       </c>
@@ -1626,7 +1619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>20</v>
       </c>
@@ -1634,7 +1627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -1645,9 +1638,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54">
-		</row>
-    <row r="55">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>20</v>
       </c>
@@ -1655,7 +1646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>43</v>
       </c>
@@ -1666,7 +1657,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1677,9 +1668,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58">
-		</row>
-    <row r="59">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -1690,9 +1679,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60">
-		</row>
-    <row r="61">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>48</v>
       </c>
@@ -1703,9 +1690,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62">
-		</row>
-    <row r="63">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1701,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>52</v>
       </c>
@@ -1727,7 +1712,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -1738,7 +1723,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>56</v>
       </c>
@@ -1749,7 +1734,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>58</v>
       </c>
@@ -1760,7 +1745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>60</v>
       </c>
@@ -1771,7 +1756,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>62</v>
       </c>
@@ -1782,7 +1767,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>64</v>
       </c>
@@ -1793,60 +1778,56 @@
         <v>65</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>66</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>67</v>
       </c>
-      <c r="C71" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
+      <c r="B75" t="s">
         <v>68</v>
       </c>
-      <c r="B73" t="s">
-        <v>49</v>
-      </c>
-      <c r="C73" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" t="s">
-        <v>22</v>
-      </c>
-      <c r="C74" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75">
-		</row>
-    <row r="76">
-      <c r="A76" t="s">
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>69</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>70</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C77" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="77">
-		</row>
-    <row r="78">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>71</v>
       </c>
@@ -1857,7 +1838,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>73</v>
       </c>
@@ -1868,7 +1849,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>75</v>
       </c>
@@ -1879,7 +1860,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>77</v>
       </c>
@@ -1890,7 +1871,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>79</v>
       </c>
@@ -1901,7 +1882,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>81</v>
       </c>
@@ -1912,7 +1893,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -1923,7 +1904,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -1934,7 +1915,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -1945,7 +1926,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>20</v>
       </c>
@@ -1953,18 +1934,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C88" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>22</v>
       </c>
@@ -1972,16 +1953,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90">
-		</row>
-    <row r="91">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92">
-		</row>
-    <row r="93">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>20</v>
       </c>
@@ -1989,12 +1966,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>22</v>
       </c>
@@ -2002,7 +1979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>20</v>
       </c>
@@ -2010,7 +1987,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -2021,7 +1998,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>22</v>
       </c>
@@ -2029,7 +2006,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>20</v>
       </c>
@@ -2037,7 +2014,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>93</v>
       </c>
@@ -2048,9 +2025,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="101">
-		</row>
-    <row r="102">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>20</v>
       </c>
@@ -2058,7 +2033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>94</v>
       </c>
@@ -2069,28 +2044,22 @@
         <v>95</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="105">
-		</row>
-    <row r="106">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="107">
-		</row>
-    <row r="108">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="109">
-		</row>
-    <row r="110">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>20</v>
       </c>
@@ -2098,12 +2067,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>22</v>
       </c>
@@ -2111,16 +2080,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113">
-		</row>
-    <row r="114">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="115">
-		</row>
-    <row r="116">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>20</v>
       </c>
@@ -2128,12 +2093,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>22</v>
       </c>
@@ -2141,14 +2106,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119">
-		</row>
-    <row r="120">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>20</v>
       </c>
@@ -2156,12 +2119,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>22</v>
       </c>
@@ -2169,7 +2132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>20</v>
       </c>
@@ -2177,14 +2140,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="126">
-		</row>
-    <row r="127">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>20</v>
       </c>
@@ -2192,7 +2153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>105</v>
       </c>
@@ -2203,28 +2164,22 @@
         <v>95</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="130">
-		</row>
-    <row r="131">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="132">
-		</row>
-    <row r="133">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="134">
-		</row>
-    <row r="135">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>20</v>
       </c>
@@ -2232,12 +2187,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>22</v>
       </c>
@@ -2245,7 +2200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>20</v>
       </c>
@@ -2253,12 +2208,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
         <v>22</v>
       </c>
@@ -2266,7 +2221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>20</v>
       </c>
@@ -2274,14 +2229,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="143">
-		</row>
-    <row r="144">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>20</v>
       </c>
@@ -2289,7 +2242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>112</v>
       </c>
@@ -2300,12 +2253,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
         <v>20</v>
       </c>
@@ -2313,14 +2266,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="149">
-		</row>
-    <row r="150">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
         <v>20</v>
       </c>
@@ -2328,7 +2279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
         <v>95</v>
       </c>
@@ -2336,12 +2287,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
         <v>20</v>
       </c>
@@ -2349,14 +2300,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="155">
-		</row>
-    <row r="156">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
         <v>20</v>
       </c>
@@ -2364,7 +2313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
         <v>95</v>
       </c>
@@ -2372,7 +2321,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
         <v>117</v>
       </c>
@@ -2380,8 +2329,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="159">
-		</row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>